--- a/hardware/pcb/Smart Switch BOM.xlsx
+++ b/hardware/pcb/Smart Switch BOM.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Code\ICAMS\zigbee-smart-switch\hardware\pcb\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F03057-5F9A-499F-AD0E-B1A92825ABA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +24,268 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="80">
+  <si>
+    <t>Coordinator</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Qty.</t>
+  </si>
+  <si>
+    <t>ESP32-C3 Super Mini</t>
+  </si>
+  <si>
+    <t>Already Have?</t>
+  </si>
+  <si>
+    <t>MCU</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>XB3-24Z8UT-J</t>
+  </si>
+  <si>
+    <t>$29.69 (10 pcs)</t>
+  </si>
+  <si>
+    <t>$23.52 (each)</t>
+  </si>
+  <si>
+    <t>Radio Module</t>
+  </si>
+  <si>
+    <t>Coordinator &amp; Joiner BOM:</t>
+  </si>
+  <si>
+    <t>3-6</t>
+  </si>
+  <si>
+    <t>WIZ850IO</t>
+  </si>
+  <si>
+    <t>Coord. Ethernet</t>
+  </si>
+  <si>
+    <t>Adafruit USB-C breakout 4090</t>
+  </si>
+  <si>
+    <t>Coord. USB-C Power</t>
+  </si>
+  <si>
+    <t>10kΩ resistor</t>
+  </si>
+  <si>
+    <t>5.1kΩ resistor</t>
+  </si>
+  <si>
+    <t>330Ω resistor</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>5mm LED</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>6mm tactile switch</t>
+  </si>
+  <si>
+    <t>Manual switch</t>
+  </si>
+  <si>
+    <t>Debug LED</t>
+  </si>
+  <si>
+    <t>Xbee RST pull-up</t>
+  </si>
+  <si>
+    <t>Relay Transistor Base connection</t>
+  </si>
+  <si>
+    <t>USB-C CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2N3904 NPN transistor </t>
+  </si>
+  <si>
+    <t>Relay switching logic</t>
+  </si>
+  <si>
+    <t>Joiner Control</t>
+  </si>
+  <si>
+    <t>Board</t>
+  </si>
+  <si>
+    <t>1x08 Female 2.54mm Header</t>
+  </si>
+  <si>
+    <t>$0.40 (each)</t>
+  </si>
+  <si>
+    <t>1x10 Female 2.00mm Header</t>
+  </si>
+  <si>
+    <t>$0.72 (each)</t>
+  </si>
+  <si>
+    <t>1x06 Female 2.54mm Header</t>
+  </si>
+  <si>
+    <t>$0.28 (each)</t>
+  </si>
+  <si>
+    <t>ESP-32 Headers</t>
+  </si>
+  <si>
+    <t>XBee3 Headers</t>
+  </si>
+  <si>
+    <t>Ethernet Headers</t>
+  </si>
+  <si>
+    <t>Joiner Control &amp; Power</t>
+  </si>
+  <si>
+    <t>USB-C Power Header</t>
+  </si>
+  <si>
+    <t>1x04 Female 2.54m Header</t>
+  </si>
+  <si>
+    <t>1x03 Female 2.54mm Header</t>
+  </si>
+  <si>
+    <t>Joiner Power &amp; Control Bridge</t>
+  </si>
+  <si>
+    <t>$0.34 (each)</t>
+  </si>
+  <si>
+    <t>AC to DC Converter</t>
+  </si>
+  <si>
+    <t>Joiner Power</t>
+  </si>
+  <si>
+    <t>30A Relay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLK-PM01 </t>
+  </si>
+  <si>
+    <t>$33.26 (10 pcs)</t>
+  </si>
+  <si>
+    <t>$0.88 (each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Songle SLA-05VDC-SL-A </t>
+  </si>
+  <si>
+    <t>Flyback Diode</t>
+  </si>
+  <si>
+    <t>$0.14 (each)</t>
+  </si>
+  <si>
+    <t>1N4007 Diode</t>
+  </si>
+  <si>
+    <t>100Ω 1W resistor</t>
+  </si>
+  <si>
+    <t>$0.21 (each)</t>
+  </si>
+  <si>
+    <t>Snubber</t>
+  </si>
+  <si>
+    <t>0.1µF X2 275VAC cap</t>
+  </si>
+  <si>
+    <t>Fuse holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuse, 6.3 x 32mm, Glass, Slow-Blow, 250V, 20A </t>
+  </si>
+  <si>
+    <t>Fuse Holder, 6.3 x 32mm, 300V, 20A</t>
+  </si>
+  <si>
+    <t>$1.12 (each)</t>
+  </si>
+  <si>
+    <t>$1.95 (each)</t>
+  </si>
+  <si>
+    <t>$0.54 (each)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuse to protect line in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screw Terminal </t>
+  </si>
+  <si>
+    <t>$0.55 (each)</t>
+  </si>
+  <si>
+    <t>Connects line in and line out</t>
+  </si>
+  <si>
+    <t>Male Wall Blades</t>
+  </si>
+  <si>
+    <t>Female Wall Blades</t>
+  </si>
+  <si>
+    <t>12 AWG Wire</t>
+  </si>
+  <si>
+    <t>Main in source</t>
+  </si>
+  <si>
+    <t>Main out source</t>
+  </si>
+  <si>
+    <t>Main connections</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -46,13 +308,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +608,567 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="2" width="7.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>20.36</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.95</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14">
+        <v>22</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>22</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{7AF628B5-7A69-4E2D-9995-33C855D081C2}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{D974D2AE-2329-4226-9DC1-754731DED559}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{EC85A96E-68CA-4E42-81BE-5A17F3374FBA}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{20F3C194-3E81-4410-809F-BEF9ED20F342}"/>
+    <hyperlink ref="A12" r:id="rId5" xr:uid="{EC27346B-D5A6-45F7-9693-680044ED2E10}"/>
+    <hyperlink ref="A13" r:id="rId6" xr:uid="{2BE98B70-1E92-4845-9AC0-6291C9C53F13}"/>
+    <hyperlink ref="A14" r:id="rId7" xr:uid="{A50C4DD2-83B7-42A2-9852-DFD4F49179DA}"/>
+    <hyperlink ref="A15" r:id="rId8" xr:uid="{2225AA5A-64FC-41B7-94DA-A350094554C3}"/>
+    <hyperlink ref="A16" r:id="rId9" xr:uid="{C11A5291-DA05-492A-B446-E647AF528D6A}"/>
+    <hyperlink ref="A17" r:id="rId10" xr:uid="{9D904776-543F-4777-8B2D-6F2D14A1C355}"/>
+    <hyperlink ref="A18" r:id="rId11" xr:uid="{A69A2742-0142-44B8-B76E-BEE71C3BF372}"/>
+    <hyperlink ref="A19" r:id="rId12" xr:uid="{7D6D9DBC-47F9-4579-8650-BADCD8D052A7}"/>
+    <hyperlink ref="A20" r:id="rId13" display="1N4007" xr:uid="{8657432C-7FDE-446A-A5B4-B8804E706645}"/>
+    <hyperlink ref="A21" r:id="rId14" xr:uid="{F1BF3145-C8C2-42D6-98C8-F82EC93114C2}"/>
+    <hyperlink ref="A22" r:id="rId15" xr:uid="{BC03FA1F-8F4C-4BFC-8E17-815AFBD581B1}"/>
+    <hyperlink ref="A24" r:id="rId16" xr:uid="{56599617-85B3-436F-9232-3D0E1F35E3B7}"/>
+    <hyperlink ref="A23" r:id="rId17" xr:uid="{4823A820-C64D-4BAB-AAD8-C4658B1D84A2}"/>
+    <hyperlink ref="A25" r:id="rId18" xr:uid="{7931AF2F-09A7-42C9-AE3D-275FFDC8E27C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId19"/>
 </worksheet>
 </file>
--- a/hardware/pcb/Smart Switch BOM.xlsx
+++ b/hardware/pcb/Smart Switch BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Code\ICAMS\zigbee-smart-switch\hardware\pcb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F03057-5F9A-499F-AD0E-B1A92825ABA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29967E3-1827-4E8C-BEA0-8AE2DB9F73F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="101">
   <si>
     <t>Coordinator</t>
   </si>
@@ -249,15 +249,6 @@
     <t>Connects line in and line out</t>
   </si>
   <si>
-    <t>Male Wall Blades</t>
-  </si>
-  <si>
-    <t>Female Wall Blades</t>
-  </si>
-  <si>
-    <t>12 AWG Wire</t>
-  </si>
-  <si>
     <t>Main in source</t>
   </si>
   <si>
@@ -265,6 +256,78 @@
   </si>
   <si>
     <t>Main connections</t>
+  </si>
+  <si>
+    <t>U.FL to RP-SMA</t>
+  </si>
+  <si>
+    <t>Male Plug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4GHZ DIPOLE ANTENNA RP-SMA </t>
+  </si>
+  <si>
+    <t>Antenna for range</t>
+  </si>
+  <si>
+    <t>Connects antenna to XBee3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 AWG Wire 10' </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female Plug </t>
+  </si>
+  <si>
+    <t>$3.76 (each)</t>
+  </si>
+  <si>
+    <t>$3.98 (each)</t>
+  </si>
+  <si>
+    <t>$6.97 (each)</t>
+  </si>
+  <si>
+    <t>$16.79 (each, 10')</t>
+  </si>
+  <si>
+    <t>$2.94 (each)</t>
+  </si>
+  <si>
+    <t>PCB Manufacturers:</t>
+  </si>
+  <si>
+    <t>Manufacturuer</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Lead time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB Way </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Circuits </t>
+  </si>
+  <si>
+    <t>EMSG</t>
+  </si>
+  <si>
+    <t>AlteraFlex</t>
+  </si>
+  <si>
+    <t>PCC</t>
+  </si>
+  <si>
+    <t>Coordinator size:</t>
+  </si>
+  <si>
+    <t>Joiner Control size:</t>
+  </si>
+  <si>
+    <t>Joiner Power Size:</t>
   </si>
 </sst>
 </file>
@@ -291,15 +354,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -307,27 +382,157 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -609,545 +814,686 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
     <col min="2" max="2" width="7.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="4" max="4" width="33.5703125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="23" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="H2" s="28"/>
+      <c r="I2" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="F3" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="O3" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="P3" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="H4" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>1</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="8">
         <v>20.36</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="F5" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="5">
         <v>1</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="10">
         <v>2.95</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="F6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <v>3</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="24" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="H7" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="5">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="26" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="H8" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="5">
         <v>2</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>2</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="5">
         <v>1</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="10">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="F12" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
         <v>22</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="F13" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="5">
         <v>22</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="F14" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="6">
         <v>3</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="F15" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="5">
         <v>2</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="10">
         <v>0.42</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="F16" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="4">
         <v>22</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="F17" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="5">
         <v>10</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="F18" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4">
         <v>10</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="F19" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="5">
         <v>10</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="F20" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="4">
         <v>10</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="F21" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="5">
         <v>10</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="F22" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="4">
         <v>10</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="F23" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="5">
         <v>10</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="F24" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="4">
         <v>20</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="F25" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="5">
+        <v>10</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="4">
+        <v>10</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="5">
+        <v>2</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="B29" s="4">
+        <v>10</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>8</v>
+      <c r="B30" s="7">
+        <v>10</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{7AF628B5-7A69-4E2D-9995-33C855D081C2}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{D974D2AE-2329-4226-9DC1-754731DED559}"/>
@@ -1167,8 +1513,18 @@
     <hyperlink ref="A24" r:id="rId16" xr:uid="{56599617-85B3-436F-9232-3D0E1F35E3B7}"/>
     <hyperlink ref="A23" r:id="rId17" xr:uid="{4823A820-C64D-4BAB-AAD8-C4658B1D84A2}"/>
     <hyperlink ref="A25" r:id="rId18" xr:uid="{7931AF2F-09A7-42C9-AE3D-275FFDC8E27C}"/>
+    <hyperlink ref="A30" r:id="rId19" xr:uid="{32C5FDA1-1E59-47E9-AC86-F5B0AC89972A}"/>
+    <hyperlink ref="A29" r:id="rId20" xr:uid="{1BBE7309-D7C7-4575-930D-DD93C0AA3635}"/>
+    <hyperlink ref="A28" r:id="rId21" xr:uid="{A1AAAABE-1E43-4443-B825-943B5D59970F}"/>
+    <hyperlink ref="A27" r:id="rId22" xr:uid="{CF64D41B-8B05-481F-96A7-68DB6E956FC4}"/>
+    <hyperlink ref="A26" r:id="rId23" xr:uid="{44D6262B-B52A-4692-AF73-869809C86489}"/>
+    <hyperlink ref="H4" r:id="rId24" xr:uid="{90283C41-A4CE-473A-8CB6-A769C4A2D877}"/>
+    <hyperlink ref="H5" r:id="rId25" xr:uid="{F3A6CF93-8AC1-44AB-8437-8A07B84FA4B5}"/>
+    <hyperlink ref="H6" r:id="rId26" xr:uid="{B8C6D6A4-3FE9-44EB-B5ED-C2C39EC96876}"/>
+    <hyperlink ref="H7" r:id="rId27" xr:uid="{FF1864B5-5D0A-4AE7-A517-D32D8836D970}"/>
+    <hyperlink ref="H8" r:id="rId28" xr:uid="{E021E953-3AE4-4EB0-B8E5-8BE13381304D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId19"/>
+  <pageSetup orientation="portrait" r:id="rId29"/>
 </worksheet>
 </file>
--- a/hardware/pcb/Smart Switch BOM.xlsx
+++ b/hardware/pcb/Smart Switch BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Code\ICAMS\zigbee-smart-switch\hardware\pcb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29967E3-1827-4E8C-BEA0-8AE2DB9F73F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A698F9A9-92A2-42ED-B451-9E97985C5C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3705" yWindow="1125" windowWidth="31185" windowHeight="18540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="119">
   <si>
     <t>Coordinator</t>
   </si>
@@ -303,9 +303,6 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>Lead time</t>
-  </si>
-  <si>
     <t xml:space="preserve">PCB Way </t>
   </si>
   <si>
@@ -321,13 +318,70 @@
     <t>PCC</t>
   </si>
   <si>
-    <t>Coordinator size:</t>
-  </si>
-  <si>
-    <t>Joiner Control size:</t>
-  </si>
-  <si>
-    <t>Joiner Power Size:</t>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>53.00mm</t>
+  </si>
+  <si>
+    <t>73.20mm</t>
+  </si>
+  <si>
+    <t>52.20mm</t>
+  </si>
+  <si>
+    <t>64.20mm</t>
+  </si>
+  <si>
+    <t>105.2mm</t>
+  </si>
+  <si>
+    <t>82.60mm</t>
+  </si>
+  <si>
+    <t>Board Sizes:</t>
+  </si>
+  <si>
+    <t>24 hours</t>
+  </si>
+  <si>
+    <t>Build time</t>
+  </si>
+  <si>
+    <t>TBD*</t>
+  </si>
+  <si>
+    <t>*TBD - email sent</t>
+  </si>
+  <si>
+    <t>2 days</t>
+  </si>
+  <si>
+    <t>Offers / Coupons</t>
+  </si>
+  <si>
+    <t>*Shipping paid once if purchased together</t>
+  </si>
+  <si>
+    <t>JLPCB</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>Shipping:</t>
+  </si>
+  <si>
+    <t>All 3 boards ordered together:</t>
+  </si>
+  <si>
+    <t>$5.00 welcome bonus</t>
+  </si>
+  <si>
+    <t>$10 off first order</t>
   </si>
 </sst>
 </file>
@@ -337,7 +391,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +403,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -374,7 +435,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -461,6 +522,204 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -470,14 +729,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -491,9 +747,6 @@
     </xf>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -525,14 +778,121 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -814,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.42578125" customWidth="1"/>
@@ -823,676 +1183,981 @@
     <col min="4" max="4" width="33.5703125" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.5703125" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" customWidth="1"/>
+    <col min="8" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="18" max="18" width="11.28515625" customWidth="1"/>
+    <col min="19" max="19" width="29.140625" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" customWidth="1"/>
+    <col min="22" max="22" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="43" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="I1" s="49"/>
+      <c r="U1" s="31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29" t="s">
+      <c r="H2" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="I2" s="68"/>
+      <c r="J2" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29" t="s">
+      <c r="K2" s="37"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29" t="s">
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="Q2" s="37"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="U2" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="W2" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4">
-        <v>10</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="B3" s="2">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="28" t="s">
+      <c r="F3" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="66" t="s">
+        <v>111</v>
+      </c>
+      <c r="J3" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="K3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="L3" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="M3" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="N3" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="P3" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q3" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="S3" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="U3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="W3" s="34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="L3" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="M3" s="30" t="s">
+      <c r="I4" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="J4" s="45">
+        <v>5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="M4" s="45">
+        <v>5</v>
+      </c>
+      <c r="N4" s="2">
+        <v>10</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="P4" s="45">
+        <v>31.16</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>10</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="S4" s="70">
+        <v>31.9</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="W4" s="35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>20.36</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="J5" s="69">
         <v>4</v>
       </c>
-      <c r="N3" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="O3" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="P3" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="5">
-        <v>10</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="K5" s="2">
+        <v>5</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="M5" s="46">
+        <v>5</v>
+      </c>
+      <c r="N5" s="2">
+        <v>10</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="P5" s="69">
+        <v>11.5</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>10</v>
+      </c>
+      <c r="R5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="S5" s="70">
+        <v>43.23</v>
+      </c>
+      <c r="U5" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="V5" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="W5" s="36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>2.95</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="K6" s="2">
+        <v>5</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="M6" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="N6" s="2">
+        <v>10</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="P6" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>10</v>
+      </c>
+      <c r="R6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="S6" s="73" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="F7" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="2">
+        <v>5</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="N7" s="2">
+        <v>10</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="P7" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>10</v>
+      </c>
+      <c r="R7" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="S7" s="73" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" s="2">
+        <v>5</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="N8" s="2">
+        <v>10</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="P8" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>10</v>
+      </c>
+      <c r="R8" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="S8" s="73" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="8">
-        <v>20.36</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="14" t="s">
+      <c r="C9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="J9" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="K9" s="33">
+        <v>5</v>
+      </c>
+      <c r="L9" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="N9" s="33">
+        <v>10</v>
+      </c>
+      <c r="O9" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="P9" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q9" s="33">
+        <v>10</v>
+      </c>
+      <c r="R9" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="S9" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3">
+        <v>2</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="K10" s="49"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2">
+        <v>22</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="26"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3">
+        <v>22</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="5">
-        <v>1</v>
-      </c>
-      <c r="C6" s="10">
-        <v>2.95</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="15" t="s">
+      <c r="F15" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3">
+        <v>2</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="4">
-        <v>3</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="14" t="s">
+      <c r="F16" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2">
         <v>22</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="C17" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="3">
+        <v>10</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="2">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="3">
+        <v>10</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="3">
+        <v>10</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="2">
+        <v>10</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="24"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="48"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="48"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="3">
+        <v>10</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="24"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="48"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="2">
         <v>20</v>
       </c>
-      <c r="B8" s="5">
+      <c r="C25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="55"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="40"/>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="48"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="3">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="55"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="40"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="48"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="2">
+        <v>10</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="53"/>
+      <c r="I27" s="26"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="3">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="4">
-        <v>1</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5">
-        <v>2</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="C28" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29" s="2">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="4">
-        <v>2</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="14" t="s">
+      <c r="F29" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="4">
+        <v>10</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="4">
-        <v>22</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="5">
-        <v>22</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="6">
-        <v>3</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="5">
-        <v>2</v>
-      </c>
-      <c r="C16" s="10">
-        <v>0.42</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="4">
-        <v>22</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="5">
-        <v>10</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="4">
-        <v>10</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="5">
-        <v>10</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="4">
-        <v>10</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="5">
-        <v>10</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="4">
-        <v>10</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="5">
-        <v>10</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="4">
-        <v>20</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="5">
-        <v>10</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" s="4">
-        <v>10</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="5">
-        <v>2</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="H28" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="4">
-        <v>10</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="7">
-        <v>10</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="H30" t="s">
-        <v>100</v>
+      <c r="F30" s="23" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
+  <mergeCells count="4">
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{7AF628B5-7A69-4E2D-9995-33C855D081C2}"/>
@@ -1519,12 +2184,13 @@
     <hyperlink ref="A27" r:id="rId22" xr:uid="{CF64D41B-8B05-481F-96A7-68DB6E956FC4}"/>
     <hyperlink ref="A26" r:id="rId23" xr:uid="{44D6262B-B52A-4692-AF73-869809C86489}"/>
     <hyperlink ref="H4" r:id="rId24" xr:uid="{90283C41-A4CE-473A-8CB6-A769C4A2D877}"/>
-    <hyperlink ref="H5" r:id="rId25" xr:uid="{F3A6CF93-8AC1-44AB-8437-8A07B84FA4B5}"/>
-    <hyperlink ref="H6" r:id="rId26" xr:uid="{B8C6D6A4-3FE9-44EB-B5ED-C2C39EC96876}"/>
-    <hyperlink ref="H7" r:id="rId27" xr:uid="{FF1864B5-5D0A-4AE7-A517-D32D8836D970}"/>
-    <hyperlink ref="H8" r:id="rId28" xr:uid="{E021E953-3AE4-4EB0-B8E5-8BE13381304D}"/>
+    <hyperlink ref="H5" r:id="rId25" xr:uid="{3F65DCF2-E8F5-468E-B0BD-09459DB68219}"/>
+    <hyperlink ref="H6" r:id="rId26" xr:uid="{6A88C52E-667C-477A-A10E-1487778C9777}"/>
+    <hyperlink ref="H7" r:id="rId27" xr:uid="{9CA317ED-95E9-42E7-BC46-26D9EE7E19F8}"/>
+    <hyperlink ref="H8" r:id="rId28" xr:uid="{6C07843E-287D-4146-997F-671E137F2730}"/>
+    <hyperlink ref="H9" r:id="rId29" xr:uid="{985BE1EA-123A-419E-8F70-78D294C7EC2D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId29"/>
+  <pageSetup orientation="portrait" r:id="rId30"/>
 </worksheet>
 </file>